--- a/results/parameter_study/significance_results.xlsx
+++ b/results/parameter_study/significance_results.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,77 +430,77 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n_pairs</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_human</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>mean_hybrid</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>mean_difference</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>std_difference</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>variance_difference</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>t_statistic</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>t_pvalue</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>t_significant</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>wilcoxon_statistic</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>wilcoxon_pvalue</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>wilcoxon_significant</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>cohens_d</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>effect_size</t>
         </is>
@@ -504,25 +516,25 @@
         <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>705.2333333333333</v>
+        <v>704.9333333333333</v>
       </c>
       <c r="D2" t="n">
-        <v>679.3666666666667</v>
+        <v>681.8166666666667</v>
       </c>
       <c r="E2" t="n">
-        <v>25.86666666666667</v>
+        <v>23.11666666666667</v>
       </c>
       <c r="F2" t="n">
-        <v>15.04509229815115</v>
+        <v>11.01476923239601</v>
       </c>
       <c r="G2" t="n">
-        <v>226.354802259887</v>
+        <v>121.3251412429379</v>
       </c>
       <c r="H2" t="n">
-        <v>13.31745491972947</v>
+        <v>16.2564395369276</v>
       </c>
       <c r="I2" t="n">
-        <v>1.971019277680793e-19</v>
+        <v>1.839667137174955e-23</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -531,13 +543,13 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.599885761511683e-11</v>
+        <v>1.605174495955631e-11</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1.71927603726601</v>
+        <v>2.09869731983828</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -558,22 +570,22 @@
         <v>709.65</v>
       </c>
       <c r="D3" t="n">
-        <v>682.7</v>
+        <v>684.4</v>
       </c>
       <c r="E3" t="n">
-        <v>26.95</v>
+        <v>25.25</v>
       </c>
       <c r="F3" t="n">
-        <v>15.56472056658228</v>
+        <v>15.19305589301971</v>
       </c>
       <c r="G3" t="n">
-        <v>242.2605263157895</v>
+        <v>230.828947368421</v>
       </c>
       <c r="H3" t="n">
-        <v>7.74341328337149</v>
+        <v>7.432437138312637</v>
       </c>
       <c r="I3" t="n">
-        <v>2.710487548539991e-07</v>
+        <v>4.911459593831129e-07</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -582,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>8.81987020419445e-05</v>
+        <v>8.782404130245518e-05</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1.731479847949349</v>
+        <v>1.661943467976106</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -609,22 +621,22 @@
         <v>581</v>
       </c>
       <c r="D4" t="n">
-        <v>562.3</v>
+        <v>563.4</v>
       </c>
       <c r="E4" t="n">
-        <v>18.7</v>
+        <v>17.6</v>
       </c>
       <c r="F4" t="n">
-        <v>7.854599725135919</v>
+        <v>7.570023986612905</v>
       </c>
       <c r="G4" t="n">
-        <v>61.69473684210525</v>
+        <v>57.30526315789474</v>
       </c>
       <c r="H4" t="n">
-        <v>10.64712974371778</v>
+        <v>10.39753545658315</v>
       </c>
       <c r="I4" t="n">
-        <v>1.898981074250028e-09</v>
+        <v>2.798547870955833e-09</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -633,13 +645,13 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8.720229793087962e-05</v>
+        <v>8.646063208626283e-05</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.380770587221287</v>
+        <v>2.324959607938423</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -657,25 +669,25 @@
         <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>825.05</v>
+        <v>824.15</v>
       </c>
       <c r="D5" t="n">
-        <v>793.1</v>
+        <v>797.65</v>
       </c>
       <c r="E5" t="n">
-        <v>31.95</v>
+        <v>26.5</v>
       </c>
       <c r="F5" t="n">
-        <v>17.45513044773279</v>
+        <v>6.303716531163434</v>
       </c>
       <c r="G5" t="n">
-        <v>304.6815789473684</v>
+        <v>39.73684210526316</v>
       </c>
       <c r="H5" t="n">
-        <v>8.185830761339027</v>
+        <v>18.80027476197696</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1896260714841e-07</v>
+        <v>9.775203775660604e-14</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -684,13 +696,13 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>8.769942375590214e-05</v>
+        <v>8.745059215649787e-05</v>
       </c>
       <c r="M5" t="b">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.830407403466292</v>
+        <v>4.203869236345416</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -713,27 +725,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>human_los</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>hybrid_los</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>difference</t>
         </is>
@@ -752,10 +764,10 @@
         <v>723</v>
       </c>
       <c r="D2" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
@@ -771,10 +783,10 @@
         <v>763</v>
       </c>
       <c r="D3" t="n">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -790,10 +802,10 @@
         <v>741</v>
       </c>
       <c r="D4" t="n">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="E4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -809,10 +821,10 @@
         <v>652</v>
       </c>
       <c r="D5" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -847,10 +859,10 @@
         <v>705</v>
       </c>
       <c r="D7" t="n">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -866,10 +878,10 @@
         <v>590</v>
       </c>
       <c r="D8" t="n">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -885,10 +897,10 @@
         <v>783</v>
       </c>
       <c r="D9" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -904,10 +916,10 @@
         <v>627</v>
       </c>
       <c r="D10" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -923,10 +935,10 @@
         <v>640</v>
       </c>
       <c r="D11" t="n">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -961,10 +973,10 @@
         <v>712</v>
       </c>
       <c r="D13" t="n">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -980,10 +992,10 @@
         <v>620</v>
       </c>
       <c r="D14" t="n">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -1018,10 +1030,10 @@
         <v>769</v>
       </c>
       <c r="D16" t="n">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="E16" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
@@ -1037,10 +1049,10 @@
         <v>654</v>
       </c>
       <c r="D17" t="n">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -1056,10 +1068,10 @@
         <v>826</v>
       </c>
       <c r="D18" t="n">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="E18" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -1075,10 +1087,10 @@
         <v>673</v>
       </c>
       <c r="D19" t="n">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E19" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1094,10 +1106,10 @@
         <v>782</v>
       </c>
       <c r="D20" t="n">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E20" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21">
@@ -1151,10 +1163,10 @@
         <v>662</v>
       </c>
       <c r="D23" t="n">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="E23" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -1170,10 +1182,10 @@
         <v>591</v>
       </c>
       <c r="D24" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="E24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1227,10 +1239,10 @@
         <v>579</v>
       </c>
       <c r="D27" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28">
@@ -1246,10 +1258,10 @@
         <v>608</v>
       </c>
       <c r="D28" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1284,10 +1296,10 @@
         <v>675</v>
       </c>
       <c r="D30" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -1303,10 +1315,10 @@
         <v>557</v>
       </c>
       <c r="D31" t="n">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="E31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -1322,10 +1334,10 @@
         <v>615</v>
       </c>
       <c r="D32" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -1360,10 +1372,10 @@
         <v>587</v>
       </c>
       <c r="D34" t="n">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="E34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -1379,10 +1391,10 @@
         <v>549</v>
       </c>
       <c r="D35" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1398,10 +1410,10 @@
         <v>616</v>
       </c>
       <c r="D36" t="n">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
@@ -1417,10 +1429,10 @@
         <v>563</v>
       </c>
       <c r="D37" t="n">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38">
@@ -1436,10 +1448,10 @@
         <v>583</v>
       </c>
       <c r="D38" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="E38" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
@@ -1474,10 +1486,10 @@
         <v>524</v>
       </c>
       <c r="D40" t="n">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E40" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
@@ -1512,10 +1524,10 @@
         <v>896</v>
       </c>
       <c r="D42" t="n">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="E42" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -1531,10 +1543,10 @@
         <v>762</v>
       </c>
       <c r="D43" t="n">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E43" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -1550,10 +1562,10 @@
         <v>832</v>
       </c>
       <c r="D44" t="n">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -1588,10 +1600,10 @@
         <v>864</v>
       </c>
       <c r="D46" t="n">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="E46" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -1607,10 +1619,10 @@
         <v>906</v>
       </c>
       <c r="D47" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="E47" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1626,10 +1638,10 @@
         <v>854</v>
       </c>
       <c r="D48" t="n">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="E48" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -1645,10 +1657,10 @@
         <v>726</v>
       </c>
       <c r="D49" t="n">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E49" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -1664,10 +1676,10 @@
         <v>873</v>
       </c>
       <c r="D50" t="n">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="E50" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51">
@@ -1683,10 +1695,10 @@
         <v>865</v>
       </c>
       <c r="D51" t="n">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E51" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52">
@@ -1702,10 +1714,10 @@
         <v>711</v>
       </c>
       <c r="D52" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="E52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="53">
@@ -1721,10 +1733,10 @@
         <v>821</v>
       </c>
       <c r="D53" t="n">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="E53" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
@@ -1740,10 +1752,10 @@
         <v>701</v>
       </c>
       <c r="D54" t="n">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="E54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
@@ -1759,10 +1771,10 @@
         <v>856</v>
       </c>
       <c r="D55" t="n">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E55" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56">
@@ -1778,10 +1790,10 @@
         <v>877</v>
       </c>
       <c r="D56" t="n">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="E56" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
@@ -1816,10 +1828,10 @@
         <v>865</v>
       </c>
       <c r="D58" t="n">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="E58" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -1835,10 +1847,10 @@
         <v>882</v>
       </c>
       <c r="D59" t="n">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="E59" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
@@ -1854,15 +1866,15 @@
         <v>725</v>
       </c>
       <c r="D60" t="n">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="E60" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>8004</v>
+        <v>77</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1870,13 +1882,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>856</v>
+        <v>838</v>
       </c>
       <c r="D61" t="n">
-        <v>756</v>
+        <v>812</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
